--- a/personal_forms/015_love_notes_collection_form--personal_forms.xlsx
+++ b/personal_forms/015_love_notes_collection_form--personal_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,36 +515,40 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Love Notes Collection Form</t>
+          <t>What's your significant other's name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>love_notes</t>
+          <t>event_date</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>love_notes</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Date of the event or occasion</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -556,18 +560,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>love_notes</t>
+          <t>event_location</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>love_notes</t>
+          <t>Location of the event or occasion</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,12 +583,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>love_notes</t>
+          <t>love_notes_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>love_notes</t>
+          <t>Describe your love for your significant other</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +606,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>love_notes_collection_form_page_2</t>
+          <t>favorite_memory</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Love Notes Collection Form</t>
+          <t>Do you have a favorite memory with your significant other?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +629,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>love_message</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>Special message or note for your significant other</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +652,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>love_story</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>Love story about your significant other</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,15 +675,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>event_location</t>
+          <t>file_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>event_location</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Attach a photo of you and your significant other</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>File type - image</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -694,12 +702,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>love_notes_collection_form_page_3</t>
+          <t>love_gift</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Love Notes Collection Form</t>
+          <t>Would you like to send a love gift to your significant other?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +725,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>love_notes_collection_form_page_4</t>
+          <t>love_notes_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Love Notes Collection Form</t>
+          <t>Additional love notes or messages</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,340 +748,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>love_notes</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>love_notes</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>love_notes_collection_form_page_5</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Love Notes Collection Form</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>love_notes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>love_notes</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>love_notes_collection_form_page_6</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Love Notes Collection Form</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>love_notes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>love_notes</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>love_notes_collection_form_page_7</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Love Notes Collection Form</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>love_notes_collection_form_page_8</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Love Notes Collection Form</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>love_notes_collection_form_page_9</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Love Notes Collection Form</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>love_notes_collection_form_page_10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Love Notes Collection Form</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>love_notes_collection_form_page_11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Love Notes Collection Form</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>love_notes_collection_form_page_12</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Love Notes Collection Form</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>love_notes_collection_form_page_13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Love Notes Collection Form</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>love_notes_collection_form_page_14</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Love Notes Collection Form</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>love_notes_collection_form_page_15</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Love Notes Collection Form</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
